--- a/output/第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx
+++ b/output/第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx
@@ -999,7 +999,7 @@
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>当方が保有しているのは、第9期計画から作成した施策別の整理（第9期施策別評価表、施策の採否・見直し基準）であり、第9期計画の本文そのものではありません。「第6期給付適正化計画」という語が施策名のかっこ書きに限られるのか、本文中に別の記載（節見出し、目標の表、事業の一覧など）があるのかは、本文で確認する必要があります。第9期計画の本文（PDF又はWord）をご提供いただければ、記載箇所をすべて拾い出して本シートを確定します（確認事項No.90）。</t>
+          <t>第9期計画の本文は業務着手時に貸与を受けて確認していますが、本シートの作成に当たっては、「第6期給付適正化計画」という語が施策名のかっこ書きに限られるのか、本文中に別の記載（節見出し、目標の表、事業の一覧など）があるのかを、記載箇所ごとに確認する必要があります。第9期計画の本文（PDF又はWord）をご提供いただければ、記載箇所をすべて拾い出して本シートを確定します（確認事項No.90）。</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の本文の提供</t>
+          <t>第9期計画の本文（電子データ）の提供</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>第9期計画における給付適正化の記載を確定するため、第9期計画の本文（PDF又はWord）をご提供いただきたい。当方が保有しているのは第9期計画から作成した施策別の整理であり、本文そのものではない。</t>
+          <t>第9期計画における給付適正化の記載を確定するため、第9期計画の本文（PDF又はWord）をご提供いただきたい。本文は業務着手時に貸与を受けて確認しているが、給付適正化に関する記載の箇所を漏れなく拾い出すには電子データによる確認を要する。</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
